--- a/output/pdf_financials_xlsx/TPX.B.xlsx
+++ b/output/pdf_financials_xlsx/TPX.B.xlsx
@@ -906,13 +906,13 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>25.4</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>35.4</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>0</v>
@@ -1656,13 +1656,13 @@
         <v>1287.8</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-62.5</v>
+        <v>-66.8</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1252.5</v>
+        <v>1227.1</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1503</v>
+        <v>1467.6</v>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
@@ -1746,13 +1746,13 @@
         <v>1579.3</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-62.5</v>
+        <v>-66.8</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1252.5</v>
+        <v>1227.1</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>1503</v>
+        <v>1467.6</v>
       </c>
       <c r="L29" s="1" t="inlineStr">
         <is>
@@ -1792,13 +1792,13 @@
         <v>17.60685856986778</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-0.4879953152449736</v>
+        <v>-0.5215693929338279</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>10.70320711667137</v>
+        <v>10.48615205817759</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>12.9268082910467</v>
+        <v>12.62234454287434</v>
       </c>
       <c r="L30" s="1" t="inlineStr">
         <is>
@@ -26373,7 +26373,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -26444,7 +26444,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">

--- a/output/pdf_financials_xlsx/TPX.B.xlsx
+++ b/output/pdf_financials_xlsx/TPX.B.xlsx
@@ -5825,19 +5825,19 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I112" s="1" t="inlineStr">
         <is>
@@ -20392,7 +20392,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -20459,7 +20463,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -23357,7 +23365,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -23424,7 +23436,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TPX.B.xlsx
+++ b/output/pdf_financials_xlsx/TPX.B.xlsx
@@ -3039,16 +3039,16 @@
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>4706.3</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>4972.6</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>5243.8</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>5491</v>
       </c>
       <c r="I56" s="1" t="inlineStr">
         <is>
@@ -3056,15 +3056,13 @@
         </is>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0</v>
+        <v>8546.1</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>8852.4</v>
+      </c>
+      <c r="L56" s="3" t="n">
+        <v>9748.4</v>
       </c>
     </row>
     <row r="57">
@@ -3089,16 +3087,16 @@
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>2317.9</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0</v>
+        <v>2492.5</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0</v>
+        <v>2656.3</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0</v>
+        <v>2800.2</v>
       </c>
       <c r="I57" s="1" t="inlineStr">
         <is>
@@ -3106,15 +3104,13 @@
         </is>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0</v>
+        <v>4101.6</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4392</v>
+      </c>
+      <c r="L57" s="3" t="n">
+        <v>4979.7</v>
       </c>
     </row>
     <row r="58">
